--- a/research/traditional_assets/database/data/macau/macau_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/macau/macau_electronics_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.111</v>
+        <v>0.0146</v>
       </c>
       <c r="E2">
-        <v>-0.0489</v>
+        <v>0.0319</v>
       </c>
       <c r="G2">
-        <v>0.05375275938189846</v>
+        <v>0.06841359773371106</v>
       </c>
       <c r="H2">
-        <v>0.05375275938189846</v>
+        <v>0.06841359773371106</v>
       </c>
       <c r="I2">
-        <v>0.04437086092715232</v>
+        <v>0.04801699716713882</v>
       </c>
       <c r="J2">
-        <v>0.04437086092715232</v>
+        <v>0.04699730182317739</v>
       </c>
       <c r="K2">
-        <v>3.37</v>
+        <v>6.18</v>
       </c>
       <c r="L2">
-        <v>0.03719646799116998</v>
+        <v>0.08753541076487252</v>
       </c>
       <c r="M2">
         <v>3.19</v>
       </c>
       <c r="N2">
-        <v>0.06431451612903226</v>
+        <v>0.07559241706161136</v>
       </c>
       <c r="O2">
-        <v>0.9465875370919881</v>
+        <v>0.5161812297734628</v>
       </c>
       <c r="P2">
         <v>3.19</v>
       </c>
       <c r="Q2">
-        <v>0.06431451612903226</v>
+        <v>0.07559241706161136</v>
       </c>
       <c r="R2">
-        <v>0.9465875370919881</v>
+        <v>0.5161812297734628</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>15.6</v>
+        <v>17.4</v>
       </c>
       <c r="V2">
-        <v>0.3145161290322581</v>
+        <v>0.4123222748815165</v>
       </c>
       <c r="W2">
-        <v>0.03812217194570135</v>
+        <v>0.06975169300225734</v>
       </c>
       <c r="X2">
-        <v>0.1286888655414828</v>
+        <v>0.1087178609740117</v>
       </c>
       <c r="Y2">
-        <v>-0.09056669359578143</v>
+        <v>-0.03896616797175433</v>
       </c>
       <c r="Z2">
-        <v>1.276056338028169</v>
+        <v>0.9671232876712328</v>
       </c>
       <c r="AA2">
-        <v>0.05661971830985915</v>
+        <v>0.04545218505090854</v>
       </c>
       <c r="AB2">
-        <v>0.1286888655414828</v>
+        <v>0.1087178609740117</v>
       </c>
       <c r="AC2">
-        <v>-0.07206914723162364</v>
+        <v>-0.06326567592310312</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-15.6</v>
+        <v>-17.4</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.4588235294117647</v>
+        <v>-0.7016129032258063</v>
       </c>
       <c r="AK2">
-        <v>-0.2136986301369863</v>
+        <v>-0.2345013477088949</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.22</v>
+        <v>-1.38</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-2.722513089005235</v>
+        <v>-3.473053892215569</v>
       </c>
       <c r="AQ2">
-        <v>-3.295081967213115</v>
+        <v>-2.456521739130435</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.111</v>
+        <v>0.0146</v>
       </c>
       <c r="E3">
-        <v>-0.0489</v>
+        <v>0.0319</v>
       </c>
       <c r="G3">
-        <v>0.05375275938189846</v>
+        <v>0.06841359773371106</v>
       </c>
       <c r="H3">
-        <v>0.05375275938189846</v>
+        <v>0.06841359773371106</v>
       </c>
       <c r="I3">
-        <v>0.04437086092715232</v>
+        <v>0.04801699716713882</v>
       </c>
       <c r="J3">
-        <v>0.04437086092715232</v>
+        <v>0.04699730182317739</v>
       </c>
       <c r="K3">
-        <v>3.37</v>
+        <v>6.18</v>
       </c>
       <c r="L3">
-        <v>0.03719646799116998</v>
+        <v>0.08753541076487252</v>
       </c>
       <c r="M3">
         <v>3.19</v>
       </c>
       <c r="N3">
-        <v>0.06431451612903226</v>
+        <v>0.07559241706161136</v>
       </c>
       <c r="O3">
-        <v>0.9465875370919881</v>
+        <v>0.5161812297734628</v>
       </c>
       <c r="P3">
         <v>3.19</v>
       </c>
       <c r="Q3">
-        <v>0.06431451612903226</v>
+        <v>0.07559241706161136</v>
       </c>
       <c r="R3">
-        <v>0.9465875370919881</v>
+        <v>0.5161812297734628</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>15.6</v>
+        <v>17.4</v>
       </c>
       <c r="V3">
-        <v>0.3145161290322581</v>
+        <v>0.4123222748815165</v>
       </c>
       <c r="W3">
-        <v>0.03812217194570135</v>
+        <v>0.06975169300225734</v>
       </c>
       <c r="X3">
-        <v>0.1286888655414828</v>
+        <v>0.1087178609740117</v>
       </c>
       <c r="Y3">
-        <v>-0.09056669359578143</v>
+        <v>-0.03896616797175433</v>
       </c>
       <c r="Z3">
-        <v>1.276056338028169</v>
+        <v>0.9671232876712328</v>
       </c>
       <c r="AA3">
-        <v>0.05661971830985915</v>
+        <v>0.04545218505090854</v>
       </c>
       <c r="AB3">
-        <v>0.1286888655414828</v>
+        <v>0.1087178609740117</v>
       </c>
       <c r="AC3">
-        <v>-0.07206914723162364</v>
+        <v>-0.06326567592310312</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-15.6</v>
+        <v>-17.4</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.4588235294117647</v>
+        <v>-0.7016129032258063</v>
       </c>
       <c r="AK3">
-        <v>-0.2136986301369863</v>
+        <v>-0.2345013477088949</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.22</v>
+        <v>-1.38</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-2.722513089005235</v>
+        <v>-3.473053892215569</v>
       </c>
       <c r="AQ3">
-        <v>-3.295081967213115</v>
+        <v>-2.456521739130435</v>
       </c>
     </row>
   </sheetData>
